--- a/vault-dalarna-university/04 ISLL/Analys/Förkunskapskrav.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Förkunskapskrav.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Förkunskapskrav" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$E$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$E$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>GEN222</t>
+          <t>EN3077</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Osannolikt kort innehåll</t>
+          <t>Refererar okänd HDa-kurs</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
+          <t>Refererad kurs hittas ej i vaulten: 'Engelska: Språkvetenskap i tal och skrift'</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN222</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3077</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>GEN3DG</t>
+          <t>GEN222</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -703,19 +703,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Osannolikt kort (21 tecken): '- Engelska I, 22,5 hp'</t>
+          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN222</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>GEN3K3</t>
+          <t>GEN3DG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -735,19 +735,19 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>AKI28Z</t>
+          <t>GEN3K3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -757,19 +757,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Osannolikt kort (24 tecken): '- Examen om minst 180 hp'</t>
+          <t>Osannolikt kort (21 tecken): '- Engelska I, 22,5 hp'</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI28Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>AKI292</t>
+          <t>AKI28Z</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -789,19 +789,19 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI292</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI28Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>GSP2JH</t>
+          <t>AKI292</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
+          <t>Osannolikt kort (24 tecken): '- Examen om minst 180 hp'</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI292</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>GSS2G8</t>
+          <t>GSP2JH</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -843,147 +843,417 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GSS2JA</t>
+          <t>GSP2YT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Osannolikt kort innehåll</t>
+          <t>Refererar okänd HDa-kurs</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
+          <t>Refererad kurs hittas ej i vaulten: 'Spanska I: Skriftlig språkfärdighet och grammatik'</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2YT</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GSS2XE</t>
+          <t>SP1050</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Osannolikt kort innehåll</t>
+          <t>Refererar okänd HDa-kurs</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
+          <t>Refererad kurs hittas ej i vaulten: 'Spanska I: Skriftlig språkfärdighet och grammatik'</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>SP1051</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Osannolikt kort innehåll</t>
+          <t>Refererar okänd HDa-kurs</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
+          <t>Refererad kurs hittas ej i vaulten: 'Spanska I: Skriftlig språkfärdighet och grammatik'</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>ASV2CP</t>
+          <t>SP1052</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Osannolikt kort innehåll</t>
+          <t>Refererar okänd HDa-kurs</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Osannolikt kort (19 tecken): '- Lärarlegitimation'</t>
+          <t>Refererad kurs hittas ej i vaulten: 'Spanska I: Skriftlig språkfärdighet och grammatik'</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1052</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>SP1053</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Refererar okänd HDa-kurs</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Refererad kurs hittas ej i vaulten: 'Spanska I: Skriftlig språkfärdighet och grammatik'</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1053</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>GSS2G8</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Osannolikt kort innehåll</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>GSS2JA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Osannolikt kort innehåll</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>GSS2XE</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Osannolikt kort innehåll</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>SS1085</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Osannolikt kort innehåll</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>ASV2CP</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Osannolikt kort innehåll</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Osannolikt kort (19 tecken): '- Lärarlegitimation'</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>ASV2CQ</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>SVE</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Osannolikt kort innehåll</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Osannolikt kort innehåll</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>Osannolikt kort (19 tecken): '- Lärarlegitimation'</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>TY1069</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Refererar okänd HDa-kurs</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Refererad kurs hittas ej i vaulten: 'Tysk grammatik och textkommentar'</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1069</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>TY2004</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Refererar okänd HDa-kurs</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Refererad kurs hittas ej i vaulten: 'Muntlig språkfärdighet med kulturkunskap II'</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2004</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>TY2007</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Refererar okänd HDa-kurs</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Refererad kurs hittas ej i vaulten: 'Muntlig språkfärdighet med kulturkunskap II'</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>TY2008</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Refererar okänd HDa-kurs</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Refererad kurs hittas ej i vaulten: 'Språk- och kulturhistoria med uppsats'</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E20"/>
+  <autoFilter ref="A1:E30"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -1023,6 +1293,26 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Förkunskapskrav.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Förkunskapskrav.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Förkunskapskrav" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$E$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,788 +472,275 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>GAR38K</t>
+          <t>EN3077</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Osannolikt kort innehåll</t>
+          <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Osannolikt kort (19 tecken): '- Arabiska I, 15 hp'</t>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Engelska: Språkvetenskap i tal och skrift'</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR38K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3077</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>GAR38L</t>
+          <t>GSP2YT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Osannolikt kort innehåll</t>
+          <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Osannolikt kort (20 tecken): '- Arabiska II, 15 hp'</t>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Spanska I: Skriftlig språkfärdighet och grammatik'</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR38L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2YT</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>GAR38M</t>
+          <t>SP1050</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Osannolikt kort innehåll</t>
+          <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Osannolikt kort (21 tecken): '- Arabiska III, 15 hp'</t>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Spanska I: Skriftlig språkfärdighet och grammatik'</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR38M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>GAR38N</t>
+          <t>SP1051</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Osannolikt kort innehåll</t>
+          <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Osannolikt kort (20 tecken): '- Arabiska IV, 15 hp'</t>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Spanska I: Skriftlig språkfärdighet och grammatik'</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR38N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>GAR39K</t>
+          <t>SP1052</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Osannolikt kort innehåll</t>
+          <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Osannolikt kort (20 tecken): '- Arabiska II, 15 hp'</t>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Spanska I: Skriftlig språkfärdighet och grammatik'</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1052</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>GAR39L</t>
+          <t>SP1053</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Osannolikt kort innehåll</t>
+          <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Osannolikt kort (19 tecken): '- Arabiska V, 15 hp'</t>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Spanska I: Skriftlig språkfärdighet och grammatik'</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1053</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>GAR39M</t>
+          <t>TY1069</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Osannolikt kort innehåll</t>
+          <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Osannolikt kort (19 tecken): '- Arabiska V, 15 hp'</t>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Tysk grammatik och textkommentar'</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1069</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>EN3077</t>
+          <t>TY2004</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Refererar okänd HDa-kurs</t>
+          <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten: 'Engelska: Språkvetenskap i tal och skrift'</t>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Muntlig språkfärdighet med kulturkunskap II'</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3077</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2004</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>GEN222</t>
+          <t>TY2007</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Osannolikt kort innehåll</t>
+          <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Muntlig språkfärdighet med kulturkunskap II'</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN222</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>GEN3DG</t>
+          <t>TY2008</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Osannolikt kort innehåll</t>
+          <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Osannolikt kort (21 tecken): '- Engelska I, 22,5 hp'</t>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Språk- och kulturhistoria med uppsats'</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>GEN3K3</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>ENA</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Osannolikt kort innehåll</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Osannolikt kort (21 tecken): '- Engelska I, 22,5 hp'</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>AKI28Z</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>KIA</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Osannolikt kort innehåll</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Osannolikt kort (24 tecken): '- Examen om minst 180 hp'</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI28Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>AKI292</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>KIA</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Osannolikt kort innehåll</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Osannolikt kort (24 tecken): '- Examen om minst 180 hp'</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI292</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>GSP2JH</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>SPA</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Osannolikt kort innehåll</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>GSP2YT</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>SPA</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Refererar okänd HDa-kurs</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Refererad kurs hittas ej i vaulten: 'Spanska I: Skriftlig språkfärdighet och grammatik'</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2YT</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>SP1050</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>SPA</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Refererar okänd HDa-kurs</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Refererad kurs hittas ej i vaulten: 'Spanska I: Skriftlig språkfärdighet och grammatik'</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>SP1051</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>SPA</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Refererar okänd HDa-kurs</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Refererad kurs hittas ej i vaulten: 'Spanska I: Skriftlig språkfärdighet och grammatik'</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>SP1052</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>SPA</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Refererar okänd HDa-kurs</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Refererad kurs hittas ej i vaulten: 'Spanska I: Skriftlig språkfärdighet och grammatik'</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1052</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>SP1053</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>SPA</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Refererar okänd HDa-kurs</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Refererad kurs hittas ej i vaulten: 'Spanska I: Skriftlig språkfärdighet och grammatik'</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1053</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>GSS2G8</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Osannolikt kort innehåll</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>GSS2JA</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Osannolikt kort innehåll</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>GSS2XE</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Osannolikt kort innehåll</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>SS1085</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Osannolikt kort innehåll</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>ASV2CP</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Osannolikt kort innehåll</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Osannolikt kort (19 tecken): '- Lärarlegitimation'</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>ASV2CQ</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Osannolikt kort innehåll</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Osannolikt kort (19 tecken): '- Lärarlegitimation'</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>TY1069</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Refererar okänd HDa-kurs</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Refererad kurs hittas ej i vaulten: 'Tysk grammatik och textkommentar'</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1069</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>TY2004</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Refererar okänd HDa-kurs</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Refererad kurs hittas ej i vaulten: 'Muntlig språkfärdighet med kulturkunskap II'</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2004</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>TY2007</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Refererar okänd HDa-kurs</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Refererad kurs hittas ej i vaulten: 'Muntlig språkfärdighet med kulturkunskap II'</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>TY2008</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Refererar okänd HDa-kurs</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Refererad kurs hittas ej i vaulten: 'Språk- och kulturhistoria med uppsats'</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E30"/>
+  <autoFilter ref="A1:E11"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -1275,44 +762,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Förkunskapskrav.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Förkunskapskrav.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Förkunskapskrav" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$E$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$E$89</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,201 +472,201 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>EN3077</t>
+          <t>AR2001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Refererar troligen nedlagd kurs</t>
+          <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Engelska: Språkvetenskap i tal och skrift'</t>
+          <t>`Arabiska VII` → `AR1013` (nedlagd 2017-10-17); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3077</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>GSP2YT</t>
+          <t>AEN25H</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Refererar troligen nedlagd kurs</t>
+          <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Spanska I: Skriftlig språkfärdighet och grammatik'</t>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2YT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25H</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>SP1050</t>
+          <t>AEN25J</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Refererar troligen nedlagd kurs</t>
+          <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Spanska I: Skriftlig språkfärdighet och grammatik'</t>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25J</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>SP1051</t>
+          <t>EN2037</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Refererar troligen nedlagd kurs</t>
+          <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Spanska I: Skriftlig språkfärdighet och grammatik'</t>
+          <t>`Introduktionskurs i modern engelsk lingvistik` → `EN1044` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2037</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SP1052</t>
+          <t>EN2046</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Refererar troligen nedlagd kurs</t>
+          <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Spanska I: Skriftlig språkfärdighet och grammatik'</t>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1052</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>SP1053</t>
+          <t>EN3070</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Refererar troligen nedlagd kurs</t>
+          <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Spanska I: Skriftlig språkfärdighet och grammatik'</t>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1053</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3070</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>TY1069</t>
+          <t>EN3072</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Refererar troligen nedlagd kurs</t>
+          <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Tysk grammatik och textkommentar'</t>
+          <t>`Engelska` → `ENC036` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1069</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3072</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>TY2004</t>
+          <t>EN3077</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -676,71 +676,2177 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Muntlig språkfärdighet med kulturkunskap II'</t>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Engelska: Språkvetenskap i tal och skrift'</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3077</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>TY2007</t>
+          <t>EN3077</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Refererar troligen nedlagd kurs</t>
+          <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Muntlig språkfärdighet med kulturkunskap II'</t>
+          <t>`Engelska` → `ENC036` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3077</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>AFR24A</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>AFR24B</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24B</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>GFR27N</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>`Franskspråkig litteratur I` → `FR1029` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27N</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>GFR27Q</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>`Franskspråkig litteratur I` → `FR1029` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>GFR27R</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>`Franskspråkig litteratur I` → `FR1029` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27R</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>GFR2KQ</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>`Franskspråkig litteratur II` → `FR1072` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>GFR2KR</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>`Franskspråkig litteratur II` → `FR1072` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KR</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>GFR2R3</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>`Franskspråkig litteratur I` → `FR1029` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>GFR35F</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>`Franskspråkig litteratur II` → `FR1072` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR35F</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>GIT2GV</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>`Italienska B` → `ITB001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2GV</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>GIT2GW</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>`Italienska B` → `ITB001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2GW</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>GIT397</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>`Italienska C` → `ITC002` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT397</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>GIT397</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>`Italiensk språkvetenskap` → `IT2005` (nedlagd 2023-12-21); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT397</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>GJP23L</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>`Japanska II` → `JP1007` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23L</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>GJP242</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>`Japanska II` → `JP1007` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP242</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>GJP243</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>`Japanska III` → `JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP243</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>GJP2MZ</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>`Japanska I` → `JP1001` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>GJP2N2</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>`Japanska II` → `JP1007` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2N2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>GJP37U</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>`Japanska II` → `JP1007` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37U</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>GJP37W</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>`Japanska III` → `JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>GJP39W</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>`Japanska III` → `JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39W</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>GJP39X</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>`Japanska III` → `JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39X</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>GJP3B2</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>`Japanska III` → `JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP3B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>AKI25K</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI25K</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>GKI2QA</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>`Kinesisk traditionell filosofi` → `KI2006` (nedlagd 2025-09-26); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2QA</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>GKI3CD</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>`Språkinlärning` → `EN3050` (nedlagd 2016-01-12); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CD</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>GRY285</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>`Ryska I` → `RY1004` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY285</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>GRY28H</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>`Ryska I` → `RY1004` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28H</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>GRY28J</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>`Ryska I` → `RY1004` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28J</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>GRY28K</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>`Ryska II` → `RY1012` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28K</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>GRY28L</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>`Ryska II` → `RY1012` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28L</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>GRY28U</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>`Ryska II` → `RY1012` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>GRY38S</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>`Ryska I` → `RY1004` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>ASP25D</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25D</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>ASP25E</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25E</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>GSP2KS</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>GSP2YT</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Refererar troligen nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Spanska I: Skriftlig språkfärdighet och grammatik'</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2YT</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>GSP2YT</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>`Spanska I` → `SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2YT</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>GSP3GW</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>SP1050</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Refererar troligen nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Spanska I: Skriftlig språkfärdighet och grammatik'</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>SP1050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>`Spanska I` → `SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>SP1051</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Refererar troligen nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Spanska I: Skriftlig språkfärdighet och grammatik'</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>SP1051</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>`Spanska I` → `SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>SP1052</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Refererar troligen nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Spanska I: Skriftlig språkfärdighet och grammatik'</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1052</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>SP1052</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>`Spanska I` → `SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1052</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>SP1053</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Refererar troligen nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Spanska I: Skriftlig språkfärdighet och grammatik'</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1053</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>SP1053</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>`Spanska I` → `SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1053</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>SP2021</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>SP2022</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>SP2023</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>SP2024</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>ASS257</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS257</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>ASS258</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS258</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>ASS28X</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS28X</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>SS3004</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>`Svenska som andraspråk` → `SSB001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3004</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>ASV29Z</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV29Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>ATY255</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY255</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>ATY256</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY256</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>ATY2B7</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>ATY2B7</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>`Den moderna tyskspråkiga lingvistikens utveckling` → `TYC002` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>ATY2B7</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>`Examensarbete` → `EN2004` (nedlagd 2011-02-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>ATY2B8</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>ATY2B8</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>`Den moderna tyskspråkiga lingvistikens utveckling` → `TYC002` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>ATY2B8</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>`Examensarbete` → `EN2004` (nedlagd 2011-02-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>GTY23C</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY23C</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>GTY2N3</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>GTY2N4</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N4</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>GTY3J5</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>GTY3J6</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J6</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>GTY3J7</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J7</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>GTY3J8</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J8</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>TY1049</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1049</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>TY1050</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>`Tysk grammatik med textkommentar` → `TYA038` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1050</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>TY1066</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>TY1069</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Refererar troligen nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Tysk grammatik och textkommentar'</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1069</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>TY1073</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1073</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>TY2004</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Refererar troligen nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Muntlig språkfärdighet med kulturkunskap II'</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2004</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>TY2007</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Refererar troligen nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Muntlig språkfärdighet med kulturkunskap II'</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
           <t>TY2008</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>TYA</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Språk- och kulturhistoria med uppsats'</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E11"/>
+  <autoFilter ref="A1:E89"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -762,6 +2868,162 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId176"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Förkunskapskrav.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Förkunskapskrav.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Förkunskapskrav" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$E$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$E$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:E83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -671,12 +671,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Refererar troligen nedlagd kurs</t>
+          <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Engelska: Språkvetenskap i tal och skrift'</t>
+          <t>`Engelska` → `ENC036` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>EN3077</t>
+          <t>AFR24A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -703,19 +703,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>`Engelska` → `ENC036` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3077</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24A</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AFR24A</t>
+          <t>AFR24B</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -735,14 +735,14 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24B</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>AFR24B</t>
+          <t>GFR27N</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -757,19 +757,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Franskspråkig litteratur I` → `FR1029` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27N</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>GFR27N</t>
+          <t>GFR27Q</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -789,14 +789,14 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27Q</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>GFR27Q</t>
+          <t>GFR27R</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -816,14 +816,14 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27R</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>GFR27R</t>
+          <t>GFR2KQ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -838,19 +838,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>`Franskspråkig litteratur I` → `FR1029` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
+          <t>`Franskspråkig litteratur II` → `FR1072` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KQ</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GFR2KQ</t>
+          <t>GFR2KR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -870,14 +870,14 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KR</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GFR2KR</t>
+          <t>GFR2R3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -892,19 +892,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>`Franskspråkig litteratur II` → `FR1072` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
+          <t>`Franskspråkig litteratur I` → `FR1029` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GFR2R3</t>
+          <t>GFR35F</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -919,24 +919,24 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>`Franskspråkig litteratur I` → `FR1029` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
+          <t>`Franskspråkig litteratur II` → `FR1072` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR35F</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GFR35F</t>
+          <t>GIT2GV</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -946,19 +946,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>`Franskspråkig litteratur II` → `FR1072` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
+          <t>`Italienska B` → `ITB001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR35F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2GV</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GIT2GV</t>
+          <t>GIT2GW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -978,14 +978,14 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2GV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2GW</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GIT2GW</t>
+          <t>GIT397</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1000,12 +1000,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>`Italienska B` → `ITB001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Italienska C` → `ITC002` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT397</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>`Italienska C` → `ITC002` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Italiensk språkvetenskap` → `IT2005` (nedlagd 2023-12-21); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GIT397</t>
+          <t>GJP23L</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1054,19 +1054,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>`Italiensk språkvetenskap` → `IT2005` (nedlagd 2023-12-21); förkunskap nämner nedlagd kurs</t>
+          <t>`Japanska II` → `JP1007` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT397</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23L</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GJP23L</t>
+          <t>GJP242</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1086,14 +1086,14 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP242</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GJP242</t>
+          <t>GJP243</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1108,19 +1108,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>`Japanska II` → `JP1007` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Japanska III` → `JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP242</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP243</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GJP243</t>
+          <t>GJP2MZ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1135,19 +1135,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>`Japanska III` → `JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Japanska I` → `JP1001` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP243</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GJP2MZ</t>
+          <t>GJP2N2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1162,19 +1162,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>`Japanska I` → `JP1001` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Japanska II` → `JP1007` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2N2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GJP2N2</t>
+          <t>GJP37U</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2N2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37U</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GJP37U</t>
+          <t>GJP37W</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1216,19 +1216,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>`Japanska II` → `JP1007` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Japanska III` → `JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GJP37W</t>
+          <t>GJP39W</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1248,14 +1248,14 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39W</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GJP39W</t>
+          <t>GJP39X</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1275,14 +1275,14 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39X</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GJP39X</t>
+          <t>GJP3B2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1302,19 +1302,19 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP3B2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GJP3B2</t>
+          <t>AKI25K</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>`Japanska III` → `JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP3B2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI25K</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>AKI25K</t>
+          <t>GKI2QA</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1351,19 +1351,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Kinesisk traditionell filosofi` → `KI2006` (nedlagd 2025-09-26); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI25K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2QA</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GKI2QA</t>
+          <t>GKI3CD</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1378,24 +1378,24 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>`Kinesisk traditionell filosofi` → `KI2006` (nedlagd 2025-09-26); förkunskap nämner nedlagd kurs</t>
+          <t>`Språkinlärning` → `EN3050` (nedlagd 2016-01-12); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2QA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CD</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GKI3CD</t>
+          <t>GRY285</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1405,19 +1405,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>`Språkinlärning` → `EN3050` (nedlagd 2016-01-12); förkunskap nämner nedlagd kurs</t>
+          <t>`Ryska I` → `RY1004` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY285</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GRY285</t>
+          <t>GRY28H</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1437,14 +1437,14 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY285</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28H</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GRY28H</t>
+          <t>GRY28J</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1464,14 +1464,14 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28J</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GRY28J</t>
+          <t>GRY28K</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1486,19 +1486,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>`Ryska I` → `RY1004` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
+          <t>`Ryska II` → `RY1012` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28K</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GRY28K</t>
+          <t>GRY28L</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1518,14 +1518,14 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28L</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GRY28L</t>
+          <t>GRY28U</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1545,14 +1545,14 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GRY28U</t>
+          <t>GRY38S</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1567,24 +1567,24 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>`Ryska II` → `RY1012` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
+          <t>`Ryska I` → `RY1004` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GRY38S</t>
+          <t>ASP25D</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1594,19 +1594,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>`Ryska I` → `RY1004` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25D</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>ASP25D</t>
+          <t>ASP25E</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1626,14 +1626,14 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25E</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>ASP25E</t>
+          <t>GSP2KS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1648,19 +1648,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GSP2KS</t>
+          <t>GSP2YT</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1675,19 +1675,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`Spanska I` → `SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2YT</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GSP2YT</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1697,24 +1697,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Refererar troligen nedlagd kurs</t>
+          <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Spanska I: Skriftlig språkfärdighet och grammatik'</t>
+          <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2YT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GSP2YT</t>
+          <t>SP1050</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1734,14 +1734,14 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2YT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>SP1051</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`Spanska I` → `SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>SP1050</t>
+          <t>SP1052</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1778,24 +1778,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Refererar troligen nedlagd kurs</t>
+          <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Spanska I: Skriftlig språkfärdighet och grammatik'</t>
+          <t>`Spanska I` → `SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1052</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>SP1050</t>
+          <t>SP1053</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1815,14 +1815,14 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1053</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>SP1051</t>
+          <t>SP2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1832,24 +1832,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Refererar troligen nedlagd kurs</t>
+          <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Spanska I: Skriftlig språkfärdighet och grammatik'</t>
+          <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2021</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>SP1051</t>
+          <t>SP2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1864,19 +1864,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>`Spanska I` → `SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2022</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>SP1052</t>
+          <t>SP2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1886,24 +1886,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Refererar troligen nedlagd kurs</t>
+          <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Spanska I: Skriftlig språkfärdighet och grammatik'</t>
+          <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1052</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2023</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>SP1052</t>
+          <t>SP2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1918,51 +1918,51 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>`Spanska I` → `SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1052</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>SP1053</t>
+          <t>ASS257</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Refererar troligen nedlagd kurs</t>
+          <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Spanska I: Skriftlig språkfärdighet och grammatik'</t>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1053</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS257</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>SP1053</t>
+          <t>ASS258</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1972,24 +1972,24 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>`Spanska I` → `SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1053</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS258</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>SP2021</t>
+          <t>ASS28X</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1999,24 +1999,24 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2021</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS28X</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>SP2022</t>
+          <t>SS3004</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2026,24 +2026,24 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`Svenska som andraspråk` → `SSB001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3004</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>SP2023</t>
+          <t>ASV29Z</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2053,24 +2053,24 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV29Z</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>SP2024</t>
+          <t>ATY255</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2080,24 +2080,24 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY255</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>ASS257</t>
+          <t>ATY256</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2112,19 +2112,19 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS257</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY256</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>ASS258</t>
+          <t>ATY2B7</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2134,24 +2134,24 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS258</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>ASS28X</t>
+          <t>ATY2B7</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2161,24 +2161,24 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Den moderna tyskspråkiga lingvistikens utveckling` → `TYC002` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS28X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>SS3004</t>
+          <t>ATY2B7</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2188,24 +2188,24 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>`Svenska som andraspråk` → `SSB001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Examensarbete` → `EN2004` (nedlagd 2011-02-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>ASV29Z</t>
+          <t>ATY2B8</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2215,19 +2215,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV29Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>ATY255</t>
+          <t>ATY2B8</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2242,19 +2242,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Den moderna tyskspråkiga lingvistikens utveckling` → `TYC002` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY255</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>ATY256</t>
+          <t>ATY2B8</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2269,19 +2269,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Examensarbete` → `EN2004` (nedlagd 2011-02-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY256</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>ATY2B7</t>
+          <t>GTY23C</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2301,14 +2301,14 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY23C</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>ATY2B7</t>
+          <t>GTY2N3</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2323,19 +2323,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>`Den moderna tyskspråkiga lingvistikens utveckling` → `TYC002` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>ATY2B7</t>
+          <t>GTY2N4</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2350,19 +2350,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>`Examensarbete` → `EN2004` (nedlagd 2011-02-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N4</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>ATY2B8</t>
+          <t>GTY3J5</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2382,14 +2382,14 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>ATY2B8</t>
+          <t>GTY3J6</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2404,19 +2404,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>`Den moderna tyskspråkiga lingvistikens utveckling` → `TYC002` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J6</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>ATY2B8</t>
+          <t>GTY3J7</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2431,19 +2431,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>`Examensarbete` → `EN2004` (nedlagd 2011-02-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J7</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GTY23C</t>
+          <t>GTY3J8</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2463,14 +2463,14 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY23C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J8</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GTY2N3</t>
+          <t>TY1049</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2490,14 +2490,14 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1049</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GTY2N4</t>
+          <t>TY1050</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2512,19 +2512,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Tysk grammatik med textkommentar` → `TYA038` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1050</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GTY3J5</t>
+          <t>TY1066</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2544,14 +2544,14 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GTY3J6</t>
+          <t>TY1069</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
+          <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Tysk grammatik och textkommentar'</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1069</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GTY3J7</t>
+          <t>TY1073</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2598,14 +2598,14 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1073</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>GTY3J8</t>
+          <t>TY2004</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2615,24 +2615,24 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
+          <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Muntlig språkfärdighet med kulturkunskap II'</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2004</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>TY1049</t>
+          <t>TY2007</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2642,24 +2642,24 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
+          <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Muntlig språkfärdighet med kulturkunskap II'</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1049</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>TY1050</t>
+          <t>TY2008</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2669,184 +2669,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
+          <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>`Tysk grammatik med textkommentar` → `TYA038` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Språk- och kulturhistoria med uppsats'</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1050</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>TY1066</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>TY1069</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Refererar troligen nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Tysk grammatik och textkommentar'</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1069</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>TY1073</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1073</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>TY2004</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Refererar troligen nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Muntlig språkfärdighet med kulturkunskap II'</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2004</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>TY2007</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Refererar troligen nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Muntlig språkfärdighet med kulturkunskap II'</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>TY2008</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Refererar troligen nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Språk- och kulturhistoria med uppsats'</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E89"/>
+  <autoFilter ref="A1:E83"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -3012,18 +2850,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId162"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId176"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Förkunskapskrav.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Förkunskapskrav.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Förkunskapskrav" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$E$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$E$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E83"/>
+  <dimension ref="A1:E85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -958,7 +958,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GIT2GW</t>
+          <t>GIT2GV</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -973,19 +973,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>`Italienska B` → `ITB001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Italienska förr och nu` → `IT1026` (nedlagd 2023-12-21); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2GV</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GIT397</t>
+          <t>GIT2GW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1000,19 +1000,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>`Italienska C` → `ITC002` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Italienska B` → `ITB001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT397</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2GW</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GIT397</t>
+          <t>GIT2GW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1027,24 +1027,24 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>`Italiensk språkvetenskap` → `IT2005` (nedlagd 2023-12-21); förkunskap nämner nedlagd kurs</t>
+          <t>`Italienska förr och nu` → `IT1026` (nedlagd 2023-12-21); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT397</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2GW</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GJP23L</t>
+          <t>GIT397</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1054,24 +1054,24 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>`Japanska II` → `JP1007` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Italienska C` → `ITC002` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT397</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GJP242</t>
+          <t>GIT397</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1081,19 +1081,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>`Japanska II` → `JP1007` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Italiensk språkvetenskap` → `IT2005` (nedlagd 2023-12-21); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP242</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT397</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GJP243</t>
+          <t>GJP23L</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1108,19 +1108,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>`Japanska III` → `JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Japanska II` → `JP1007` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP243</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23L</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GJP2MZ</t>
+          <t>GJP242</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1135,19 +1135,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>`Japanska I` → `JP1001` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Japanska II` → `JP1007` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP242</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GJP2N2</t>
+          <t>GJP243</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1162,19 +1162,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>`Japanska II` → `JP1007` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Japanska III` → `JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2N2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP243</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GJP37U</t>
+          <t>GJP2MZ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1189,19 +1189,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>`Japanska II` → `JP1007` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Japanska I` → `JP1001` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GJP37W</t>
+          <t>GJP2N2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1216,19 +1216,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>`Japanska III` → `JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Japanska II` → `JP1007` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2N2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GJP39W</t>
+          <t>GJP37U</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1243,19 +1243,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>`Japanska III` → `JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Japanska II` → `JP1007` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37U</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GJP39X</t>
+          <t>GJP37W</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1275,14 +1275,14 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GJP3B2</t>
+          <t>GJP39W</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1302,19 +1302,19 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP3B2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39W</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>AKI25K</t>
+          <t>GJP39X</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1324,24 +1324,24 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Japanska III` → `JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI25K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39X</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GKI2QA</t>
+          <t>GJP3B2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1351,19 +1351,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>`Kinesisk traditionell filosofi` → `KI2006` (nedlagd 2025-09-26); förkunskap nämner nedlagd kurs</t>
+          <t>`Japanska III` → `JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2QA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP3B2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GKI3CD</t>
+          <t>AKI25K</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1378,24 +1378,24 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>`Språkinlärning` → `EN3050` (nedlagd 2016-01-12); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI25K</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GRY285</t>
+          <t>GKI2QA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1405,24 +1405,24 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>`Ryska I` → `RY1004` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
+          <t>`Kinesisk traditionell filosofi` → `KI2006` (nedlagd 2025-09-26); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY285</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2QA</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GRY28H</t>
+          <t>GKI3CD</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1432,19 +1432,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>`Ryska I` → `RY1004` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
+          <t>`Språkinlärning` → `EN3050` (nedlagd 2016-01-12); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CD</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GRY28J</t>
+          <t>GRY285</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1464,14 +1464,14 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY285</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GRY28K</t>
+          <t>GRY28H</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1486,19 +1486,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>`Ryska II` → `RY1012` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
+          <t>`Ryska I` → `RY1004` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28H</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GRY28L</t>
+          <t>GRY28J</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1513,19 +1513,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>`Ryska II` → `RY1012` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
+          <t>`Ryska I` → `RY1004` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28J</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GRY28U</t>
+          <t>GRY28K</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1545,14 +1545,14 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28K</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GRY38S</t>
+          <t>GRY28L</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1567,24 +1567,24 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>`Ryska I` → `RY1004` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
+          <t>`Ryska II` → `RY1012` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28L</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>ASP25D</t>
+          <t>GRY28U</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1594,24 +1594,24 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Ryska II` → `RY1012` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>ASP25E</t>
+          <t>GRY38S</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1621,19 +1621,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Ryska I` → `RY1004` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GSP2KS</t>
+          <t>ASP25D</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1648,19 +1648,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25D</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GSP2YT</t>
+          <t>ASP25E</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1675,19 +1675,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>`Spanska I` → `SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2YT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25E</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>GSP2KS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1707,14 +1707,14 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>SP1050</t>
+          <t>GSP2YT</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1734,14 +1734,14 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2YT</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>SP1051</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>`Spanska I` → `SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>SP1052</t>
+          <t>SP1050</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1788,14 +1788,14 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1052</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>SP1053</t>
+          <t>SP1051</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1815,14 +1815,14 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1053</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>SP2021</t>
+          <t>SP1052</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`Spanska I` → `SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2021</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1052</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>SP2022</t>
+          <t>SP1053</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1864,19 +1864,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`Spanska I` → `SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1053</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>SP2023</t>
+          <t>SP2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1896,14 +1896,14 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2021</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>SP2024</t>
+          <t>SP2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1923,19 +1923,19 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2022</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>ASS257</t>
+          <t>SP2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1945,24 +1945,24 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS257</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2023</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>ASS258</t>
+          <t>SP2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1972,19 +1972,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS258</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>ASS28X</t>
+          <t>ASS257</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2004,14 +2004,14 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS28X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS257</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>SS3004</t>
+          <t>ASS258</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2026,24 +2026,24 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>`Svenska som andraspråk` → `SSB001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS258</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>ASV29Z</t>
+          <t>ASS28X</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2058,19 +2058,19 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV29Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS28X</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>ATY255</t>
+          <t>SS3004</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2080,19 +2080,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Svenska som andraspråk` → `SSB001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY255</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3004</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>ATY256</t>
+          <t>ATY255</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2112,14 +2112,14 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY256</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY255</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>ATY2B7</t>
+          <t>ATY256</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY256</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>`Den moderna tyskspråkiga lingvistikens utveckling` → `TYC002` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Tyskspråkig litteratur och litteraturvetenskap` → `TY2003` (nedlagd 2011-02-10); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>`Examensarbete` → `EN2004` (nedlagd 2011-02-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Den moderna tyskspråkiga lingvistikens utveckling` → `TYC002` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>ATY2B8</t>
+          <t>ATY2B7</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2215,12 +2215,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Examensarbete` → `EN2004` (nedlagd 2011-02-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>`Den moderna tyskspråkiga lingvistikens utveckling` → `TYC002` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Tyskspråkig litteratur och litteraturvetenskap` → `TY2003` (nedlagd 2011-02-10); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>`Examensarbete` → `EN2004` (nedlagd 2011-02-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Den moderna tyskspråkiga lingvistikens utveckling` → `TYC002` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -2281,7 +2281,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GTY23C</t>
+          <t>ATY2B8</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2296,19 +2296,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Examensarbete` → `EN2004` (nedlagd 2011-02-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY23C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GTY2N3</t>
+          <t>GTY23C</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2328,14 +2328,14 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY23C</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GTY2N4</t>
+          <t>GTY2N3</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2355,14 +2355,14 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GTY3J5</t>
+          <t>GTY2N4</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2382,14 +2382,14 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N4</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GTY3J6</t>
+          <t>GTY3J5</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2409,14 +2409,14 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GTY3J7</t>
+          <t>GTY3J6</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2436,14 +2436,14 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J6</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GTY3J8</t>
+          <t>GTY3J7</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2463,14 +2463,14 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J7</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>TY1049</t>
+          <t>GTY3J8</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2490,14 +2490,14 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1049</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J8</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>TY1050</t>
+          <t>TY1049</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2512,19 +2512,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>`Tysk grammatik med textkommentar` → `TYA038` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1049</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>TY1066</t>
+          <t>TY1050</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2539,19 +2539,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Tysk grammatik med textkommentar` → `TYA038` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1050</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>TY1069</t>
+          <t>TY1066</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Refererar troligen nedlagd kurs</t>
+          <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Tysk grammatik och textkommentar'</t>
+          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1069</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>TY1073</t>
+          <t>TY1069</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2588,24 +2588,24 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
+          <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Tysk grammatik och textkommentar'</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1073</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1069</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>TY2004</t>
+          <t>TY1073</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2615,24 +2615,24 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Refererar troligen nedlagd kurs</t>
+          <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Muntlig språkfärdighet med kulturkunskap II'</t>
+          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1073</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>TY2007</t>
+          <t>TY2004</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2652,39 +2652,93 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2004</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>TY2007</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Refererar troligen nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Muntlig språkfärdighet med kulturkunskap II'</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>TY2007</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>`Tyskspråkig skönlitteratur och litteraturhistoria` → `TYB013` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
           <t>TY2008</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>TYA</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Språk- och kulturhistoria med uppsats'</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E83"/>
+  <autoFilter ref="A1:E85"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -2850,6 +2904,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId162"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId168"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Förkunskapskrav.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Förkunskapskrav.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Förkunskapskrav" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$E$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$G$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,14 +432,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E85"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,15 +457,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Fastställd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Reviderad</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Detalj</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Länk</t>
         </is>
@@ -482,15 +494,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
+          <t>2011-11-29</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>2020-07-03</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>`Arabiska VII` → `AR1013` (nedlagd 2017-10-17); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
@@ -509,15 +531,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+          <t>2020-03-12</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25H</t>
         </is>
@@ -536,15 +564,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+          <t>2020-03-12</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25J</t>
         </is>
@@ -563,15 +597,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+          <t>2014-09-17</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>`Introduktionskurs i modern engelsk lingvistik` → `EN1044` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2037</t>
         </is>
@@ -590,15 +630,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+          <t>2016-02-05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
         </is>
@@ -617,15 +663,21 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+          <t>2015-03-12</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3070</t>
         </is>
@@ -644,15 +696,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
+          <t>2015-03-16</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2017-03-13</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>`Engelska` → `ENC036` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3072</t>
         </is>
@@ -671,15 +733,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+          <t>2017-03-13</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>`Engelska` → `ENC036` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3077</t>
         </is>
@@ -698,15 +766,21 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24A</t>
         </is>
@@ -725,15 +799,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24B</t>
         </is>
@@ -752,15 +832,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+          <t>2019-03-07</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>`Franskspråkig litteratur I` → `FR1029` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27N</t>
         </is>
@@ -779,15 +865,21 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+          <t>2019-03-07</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>`Franskspråkig litteratur I` → `FR1029` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27Q</t>
         </is>
@@ -806,15 +898,21 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+          <t>2019-03-07</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>`Franskspråkig litteratur I` → `FR1029` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27R</t>
         </is>
@@ -833,15 +931,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+          <t>2020-11-11</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>`Franskspråkig litteratur II` → `FR1072` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KQ</t>
         </is>
@@ -860,15 +964,21 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+          <t>2020-11-11</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>`Franskspråkig litteratur II` → `FR1072` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KR</t>
         </is>
@@ -887,15 +997,21 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+          <t>2021-09-06</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>`Franskspråkig litteratur I` → `FR1029` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R3</t>
         </is>
@@ -914,15 +1030,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>`Franskspråkig litteratur II` → `FR1072` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR35F</t>
         </is>
@@ -941,15 +1063,25 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
+          <t>2020-06-03</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>`Italienska B` → `ITB001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2GV</t>
         </is>
@@ -968,15 +1100,25 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
+          <t>2020-06-03</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>`Italienska förr och nu` → `IT1026` (nedlagd 2023-12-21); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2GV</t>
         </is>
@@ -995,15 +1137,25 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
+          <t>2020-06-03</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>`Italienska B` → `ITB001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2GW</t>
         </is>
@@ -1022,15 +1174,25 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
+          <t>2020-06-03</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>`Italienska förr och nu` → `IT1026` (nedlagd 2023-12-21); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2GW</t>
         </is>
@@ -1049,15 +1211,21 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>`Italienska C` → `ITC002` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT397</t>
         </is>
@@ -1076,15 +1244,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>`Italiensk språkvetenskap` → `IT2005` (nedlagd 2023-12-21); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT397</t>
         </is>
@@ -1103,15 +1277,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+          <t>2018-08-23</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>`Japanska II` → `JP1007` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23L</t>
         </is>
@@ -1130,15 +1310,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+          <t>2018-08-23</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>`Japanska II` → `JP1007` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP242</t>
         </is>
@@ -1157,15 +1343,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
+          <t>2018-08-23</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>`Japanska III` → `JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP243</t>
         </is>
@@ -1184,15 +1376,21 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+          <t>2021-03-04</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>`Japanska I` → `JP1001` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
         </is>
@@ -1211,15 +1409,21 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
+          <t>2021-03-04</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>`Japanska II` → `JP1007` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2N2</t>
         </is>
@@ -1238,15 +1442,21 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
+          <t>2023-12-04</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>`Japanska II` → `JP1007` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37U</t>
         </is>
@@ -1265,15 +1475,21 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
+          <t>2023-12-04</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>`Japanska III` → `JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
         </is>
@@ -1292,15 +1508,21 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>`Japanska III` → `JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39W</t>
         </is>
@@ -1319,15 +1541,21 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>`Japanska III` → `JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39X</t>
         </is>
@@ -1346,15 +1574,21 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
+          <t>2024-04-26</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>`Japanska III` → `JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP3B2</t>
         </is>
@@ -1373,15 +1607,21 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
+          <t>2020-03-12</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI25K</t>
         </is>
@@ -1400,15 +1640,21 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
+          <t>2021-05-26</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>`Kinesisk traditionell filosofi` → `KI2006` (nedlagd 2025-09-26); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2QA</t>
         </is>
@@ -1427,15 +1673,21 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>`Språkinlärning` → `EN3050` (nedlagd 2016-01-12); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CD</t>
         </is>
@@ -1454,15 +1706,21 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
+          <t>2019-03-11</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>`Ryska I` → `RY1004` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY285</t>
         </is>
@@ -1481,15 +1739,21 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
+          <t>2019-03-14</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>`Ryska I` → `RY1004` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28H</t>
         </is>
@@ -1508,15 +1772,21 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
+          <t>2019-03-14</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>`Ryska I` → `RY1004` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28J</t>
         </is>
@@ -1535,15 +1805,21 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
+          <t>2019-03-14</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>`Ryska II` → `RY1012` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28K</t>
         </is>
@@ -1562,15 +1838,21 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
+          <t>2019-03-14</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>`Ryska II` → `RY1012` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28L</t>
         </is>
@@ -1589,15 +1871,21 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
+          <t>2019-03-25</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>`Ryska II` → `RY1012` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
         </is>
@@ -1616,15 +1904,21 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>`Ryska I` → `RY1004` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
         </is>
@@ -1643,15 +1937,21 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25D</t>
         </is>
@@ -1670,15 +1970,21 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25E</t>
         </is>
@@ -1697,15 +2003,21 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
+          <t>2020-11-20</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
         </is>
@@ -1724,15 +2036,21 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
+          <t>2022-11-29</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>`Spanska I` → `SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2YT</t>
         </is>
@@ -1751,15 +2069,21 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
@@ -1778,15 +2102,21 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
+          <t>2017-06-15</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>`Spanska I` → `SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
         </is>
@@ -1805,15 +2135,21 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
+          <t>2017-06-15</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>`Spanska I` → `SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
         </is>
@@ -1832,15 +2168,21 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
+          <t>2017-06-15</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>`Spanska I` → `SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1052</t>
         </is>
@@ -1859,15 +2201,21 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
+          <t>2017-06-15</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>`Spanska I` → `SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1053</t>
         </is>
@@ -1886,15 +2234,21 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
+          <t>2018-02-12</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2021</t>
         </is>
@@ -1913,15 +2267,21 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
+          <t>2018-02-12</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2022</t>
         </is>
@@ -1940,15 +2300,21 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
+          <t>2018-02-12</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2023</t>
         </is>
@@ -1967,15 +2333,21 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
+          <t>2018-02-12</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
         </is>
@@ -1994,15 +2366,21 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS257</t>
         </is>
@@ -2021,15 +2399,21 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
         <is>
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS258</t>
         </is>
@@ -2048,15 +2432,21 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
+          <t>2023-05-22</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
         <is>
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS28X</t>
         </is>
@@ -2075,15 +2465,21 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
+          <t>2014-04-11</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>`Svenska som andraspråk` → `SSB001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3004</t>
         </is>
@@ -2102,15 +2498,21 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
         <is>
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY255</t>
         </is>
@@ -2129,15 +2531,21 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
         <is>
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY256</t>
         </is>
@@ -2156,15 +2564,21 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
         <is>
           <t>`Tyskspråkig litteratur och litteraturvetenskap` → `TY2003` (nedlagd 2011-02-10); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
         </is>
@@ -2183,15 +2597,21 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
         <is>
           <t>`Den moderna tyskspråkiga lingvistikens utveckling` → `TYC002` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
         </is>
@@ -2210,15 +2630,21 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
         <is>
           <t>`Examensarbete` → `EN2004` (nedlagd 2011-02-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
         </is>
@@ -2237,15 +2663,21 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
         <is>
           <t>`Tyskspråkig litteratur och litteraturvetenskap` → `TY2003` (nedlagd 2011-02-10); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
         </is>
@@ -2264,15 +2696,21 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>`Den moderna tyskspråkiga lingvistikens utveckling` → `TYC002` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
         </is>
@@ -2291,15 +2729,21 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
         <is>
           <t>`Examensarbete` → `EN2004` (nedlagd 2011-02-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
         </is>
@@ -2318,15 +2762,21 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
+          <t>2018-06-05</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY23C</t>
         </is>
@@ -2345,15 +2795,21 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
+          <t>2021-03-04</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
         <is>
           <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
         </is>
@@ -2372,15 +2828,21 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
+          <t>2021-03-04</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
         <is>
           <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N4</t>
         </is>
@@ -2399,15 +2861,21 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
         <is>
           <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
         </is>
@@ -2426,15 +2894,21 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
         <is>
           <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J6</t>
         </is>
@@ -2453,15 +2927,21 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J7</t>
         </is>
@@ -2480,15 +2960,21 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
         <is>
           <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J8</t>
         </is>
@@ -2507,15 +2993,25 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t>2013-08-01</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1049</t>
         </is>
@@ -2534,15 +3030,25 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
           <t>`Tysk grammatik med textkommentar` → `TYA038` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1050</t>
         </is>
@@ -2561,15 +3067,25 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
+          <t>2013-11-04</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
           <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
         </is>
@@ -2588,15 +3104,21 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
+          <t>2016-02-11</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
           <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Tysk grammatik och textkommentar'</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1069</t>
         </is>
@@ -2615,15 +3137,21 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
+          <t>2017-02-13</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
         <is>
           <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1073</t>
         </is>
@@ -2642,15 +3170,25 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
+          <t>2008-05-29</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2013-08-01</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
           <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Muntlig språkfärdighet med kulturkunskap II'</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2004</t>
         </is>
@@ -2669,15 +3207,25 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
           <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Muntlig språkfärdighet med kulturkunskap II'</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
         </is>
@@ -2696,15 +3244,25 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
           <t>`Tyskspråkig skönlitteratur och litteraturhistoria` → `TYB013` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
         </is>
@@ -2723,191 +3281,201 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
           <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Språk- och kulturhistoria med uppsats'</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E85"/>
+  <autoFilter ref="A1:G85"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId124"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId134"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId146"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId150"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId152"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId154"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId156"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId158"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId160"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId162"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId166"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId168"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Förkunskapskrav.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Förkunskapskrav.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Förkunskapskrav" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$G$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$G$88</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2092,7 +2092,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>SP1050</t>
+          <t>GSP3KT</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2017-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -2118,14 +2118,14 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KT</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>SP1051</t>
+          <t>GSP3KU</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2017-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -2151,14 +2151,14 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KU</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>SP1052</t>
+          <t>GSP3KV</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2017-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -2184,14 +2184,14 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1052</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KV</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>SP1053</t>
+          <t>SP1050</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2217,14 +2217,14 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1053</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>SP2021</t>
+          <t>SP1051</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2018-02-12</t>
+          <t>2017-06-15</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -2245,19 +2245,19 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`Spanska I` → `SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2021</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>SP2022</t>
+          <t>SP1052</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2018-02-12</t>
+          <t>2017-06-15</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -2278,19 +2278,19 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`Spanska I` → `SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1052</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>SP2023</t>
+          <t>SP1053</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2018-02-12</t>
+          <t>2017-06-15</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -2311,19 +2311,19 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`Spanska I` → `SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1053</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>SP2024</t>
+          <t>SP2021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2349,24 +2349,24 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2021</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>ASS257</t>
+          <t>SP2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2018-02-12</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -2377,29 +2377,29 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS257</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2022</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>ASS258</t>
+          <t>SP2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2018-02-12</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -2410,29 +2410,29 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS258</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2023</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>ASS28X</t>
+          <t>SP2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
+          <t>2018-02-12</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -2443,19 +2443,19 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS28X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>SS3004</t>
+          <t>ASS257</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2014-04-11</t>
+          <t>2020-03-11</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -2476,24 +2476,24 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>`Svenska som andraspråk` → `SSB001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS257</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>ATY255</t>
+          <t>ASS258</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2514,24 +2514,24 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY255</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS258</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>ATY256</t>
+          <t>ASS28X</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -2547,24 +2547,24 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY256</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS28X</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>ATY2B7</t>
+          <t>SS3004</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2014-04-11</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -2575,19 +2575,19 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>`Tyskspråkig litteratur och litteraturvetenskap` → `TY2003` (nedlagd 2011-02-10); förkunskap nämner nedlagd kurs</t>
+          <t>`Svenska som andraspråk` → `SSB001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3004</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>ATY2B7</t>
+          <t>ATY255</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2020-03-11</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -2608,19 +2608,19 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>`Den moderna tyskspråkiga lingvistikens utveckling` → `TYC002` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY255</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>ATY2B7</t>
+          <t>ATY256</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2020-03-11</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2641,19 +2641,19 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>`Examensarbete` → `EN2004` (nedlagd 2011-02-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY256</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>ATY2B8</t>
+          <t>ATY2B7</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2679,14 +2679,14 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>ATY2B8</t>
+          <t>ATY2B7</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2712,14 +2712,14 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>ATY2B8</t>
+          <t>ATY2B7</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2745,14 +2745,14 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GTY23C</t>
+          <t>ATY2B8</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2018-06-05</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -2773,19 +2773,19 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Tyskspråkig litteratur och litteraturvetenskap` → `TY2003` (nedlagd 2011-02-10); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY23C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GTY2N3</t>
+          <t>ATY2B8</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -2806,19 +2806,19 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Den moderna tyskspråkiga lingvistikens utveckling` → `TYC002` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GTY2N4</t>
+          <t>ATY2B8</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -2839,19 +2839,19 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Examensarbete` → `EN2004` (nedlagd 2011-02-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GTY3J5</t>
+          <t>GTY23C</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2018-06-05</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -2877,14 +2877,14 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY23C</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GTY3J6</t>
+          <t>GTY2N3</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -2910,14 +2910,14 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GTY3J7</t>
+          <t>GTY2N4</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -2943,14 +2943,14 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N4</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GTY3J8</t>
+          <t>GTY3J5</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2976,14 +2976,14 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>TY1049</t>
+          <t>GTY3J6</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2993,14 +2993,10 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>2013-08-01</t>
-        </is>
-      </c>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -3013,14 +3009,14 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1049</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J6</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>TY1050</t>
+          <t>GTY3J7</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3030,14 +3026,10 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -3045,19 +3037,19 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>`Tysk grammatik med textkommentar` → `TYA038` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J7</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>TY1066</t>
+          <t>GTY3J8</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3067,14 +3059,10 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2013-11-04</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -3087,14 +3075,14 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J8</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>TY1069</t>
+          <t>TY1049</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3104,30 +3092,34 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2016-02-11</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2013-08-01</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Refererar troligen nedlagd kurs</t>
+          <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Tysk grammatik och textkommentar'</t>
+          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1069</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1049</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>TY1073</t>
+          <t>TY1050</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3137,10 +3129,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2017-02-13</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -3148,19 +3144,19 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Tysk grammatik med textkommentar` → `TYA038` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1073</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1050</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>TY2004</t>
+          <t>TY1066</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3170,34 +3166,34 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2008-05-29</t>
+          <t>2013-11-04</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2013-08-01</t>
+          <t>2019-12-20</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Refererar troligen nedlagd kurs</t>
+          <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Muntlig språkfärdighet med kulturkunskap II'</t>
+          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>TY2007</t>
+          <t>TY1069</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3207,14 +3203,10 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
+          <t>2016-02-11</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>Refererar troligen nedlagd kurs</t>
@@ -3222,19 +3214,19 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Muntlig språkfärdighet med kulturkunskap II'</t>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Tysk grammatik och textkommentar'</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1069</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>TY2007</t>
+          <t>TY1073</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3244,14 +3236,10 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
+          <t>2017-02-13</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -3259,54 +3247,165 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>`Tyskspråkig skönlitteratur och litteraturhistoria` → `TYB013` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1073</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>TY2004</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2008-05-29</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2013-08-01</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Refererar troligen nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Muntlig språkfärdighet med kulturkunskap II'</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2004</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>TY2007</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Refererar troligen nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Muntlig språkfärdighet med kulturkunskap II'</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>TY2007</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>`Tyskspråkig skönlitteratur och litteraturhistoria` → `TYB013` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
           <t>TY2008</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>TYA</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>2012-05-21</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>2019-12-20</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Språk- och kulturhistoria med uppsats'</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G85"/>
+  <autoFilter ref="A1:G88"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -3476,6 +3575,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId166"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId174"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Förkunskapskrav.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Förkunskapskrav.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Förkunskapskrav" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$G$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$H$88</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:H88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,8 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="70" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,6 +478,11 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Förslag</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Länk</t>
         </is>
       </c>
@@ -512,7 +518,12 @@
           <t>`Arabiska VII` → `AR1013` (nedlagd 2017-10-17); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>`AR1013` (nedlagd 2017-10-17); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
@@ -545,7 +556,12 @@
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25H</t>
         </is>
@@ -578,7 +594,12 @@
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25J</t>
         </is>
@@ -611,7 +632,12 @@
           <t>`Introduktionskurs i modern engelsk lingvistik` → `EN1044` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>`EN1044` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2037</t>
         </is>
@@ -644,7 +670,12 @@
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
         </is>
@@ -677,7 +708,12 @@
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3070</t>
         </is>
@@ -714,7 +750,12 @@
           <t>`Engelska` → `ENC036` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>`ENC036` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3072</t>
         </is>
@@ -747,7 +788,12 @@
           <t>`Engelska` → `ENC036` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>`ENC036` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3077</t>
         </is>
@@ -780,7 +826,12 @@
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24A</t>
         </is>
@@ -813,7 +864,12 @@
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24B</t>
         </is>
@@ -846,7 +902,12 @@
           <t>`Franskspråkig litteratur I` → `FR1029` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>`FR1029` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27N</t>
         </is>
@@ -879,7 +940,12 @@
           <t>`Franskspråkig litteratur I` → `FR1029` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>`FR1029` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27Q</t>
         </is>
@@ -912,7 +978,12 @@
           <t>`Franskspråkig litteratur I` → `FR1029` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>`FR1029` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27R</t>
         </is>
@@ -945,7 +1016,12 @@
           <t>`Franskspråkig litteratur II` → `FR1072` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>`FR1072` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KQ</t>
         </is>
@@ -978,7 +1054,12 @@
           <t>`Franskspråkig litteratur II` → `FR1072` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>`FR1072` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KR</t>
         </is>
@@ -1011,7 +1092,12 @@
           <t>`Franskspråkig litteratur I` → `FR1029` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>`FR1029` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R3</t>
         </is>
@@ -1044,7 +1130,12 @@
           <t>`Franskspråkig litteratur II` → `FR1072` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>`FR1072` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR35F</t>
         </is>
@@ -1081,7 +1172,12 @@
           <t>`Italienska B` → `ITB001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>`ITB001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2GV</t>
         </is>
@@ -1118,7 +1214,12 @@
           <t>`Italienska förr och nu` → `IT1026` (nedlagd 2023-12-21); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>`IT1026` (nedlagd 2023-12-21); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2GV</t>
         </is>
@@ -1155,7 +1256,12 @@
           <t>`Italienska B` → `ITB001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>`ITB001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2GW</t>
         </is>
@@ -1192,7 +1298,12 @@
           <t>`Italienska förr och nu` → `IT1026` (nedlagd 2023-12-21); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>`IT1026` (nedlagd 2023-12-21); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2GW</t>
         </is>
@@ -1225,7 +1336,12 @@
           <t>`Italienska C` → `ITC002` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>`ITC002` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT397</t>
         </is>
@@ -1258,7 +1374,12 @@
           <t>`Italiensk språkvetenskap` → `IT2005` (nedlagd 2023-12-21); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>`IT2005` (nedlagd 2023-12-21); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT397</t>
         </is>
@@ -1291,7 +1412,12 @@
           <t>`Japanska II` → `JP1007` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>`JP1007` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23L</t>
         </is>
@@ -1324,7 +1450,12 @@
           <t>`Japanska II` → `JP1007` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>`JP1007` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP242</t>
         </is>
@@ -1357,7 +1488,12 @@
           <t>`Japanska III` → `JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>`JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP243</t>
         </is>
@@ -1390,7 +1526,12 @@
           <t>`Japanska I` → `JP1001` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>`JP1001` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
         </is>
@@ -1423,7 +1564,12 @@
           <t>`Japanska II` → `JP1007` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>`JP1007` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2N2</t>
         </is>
@@ -1456,7 +1602,12 @@
           <t>`Japanska II` → `JP1007` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>`JP1007` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37U</t>
         </is>
@@ -1489,7 +1640,12 @@
           <t>`Japanska III` → `JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>`JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
         </is>
@@ -1522,7 +1678,12 @@
           <t>`Japanska III` → `JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>`JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39W</t>
         </is>
@@ -1555,7 +1716,12 @@
           <t>`Japanska III` → `JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>`JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39X</t>
         </is>
@@ -1588,7 +1754,12 @@
           <t>`Japanska III` → `JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>`JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP3B2</t>
         </is>
@@ -1621,7 +1792,12 @@
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI25K</t>
         </is>
@@ -1654,7 +1830,12 @@
           <t>`Kinesisk traditionell filosofi` → `KI2006` (nedlagd 2025-09-26); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>`KI2006` (nedlagd 2025-09-26); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2QA</t>
         </is>
@@ -1687,7 +1868,12 @@
           <t>`Språkinlärning` → `EN3050` (nedlagd 2016-01-12); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>`EN3050` (nedlagd 2016-01-12); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CD</t>
         </is>
@@ -1720,7 +1906,12 @@
           <t>`Ryska I` → `RY1004` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>`RY1004` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY285</t>
         </is>
@@ -1753,7 +1944,12 @@
           <t>`Ryska I` → `RY1004` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>`RY1004` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28H</t>
         </is>
@@ -1786,7 +1982,12 @@
           <t>`Ryska I` → `RY1004` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>`RY1004` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28J</t>
         </is>
@@ -1819,7 +2020,12 @@
           <t>`Ryska II` → `RY1012` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>`RY1012` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28K</t>
         </is>
@@ -1852,7 +2058,12 @@
           <t>`Ryska II` → `RY1012` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>`RY1012` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28L</t>
         </is>
@@ -1885,7 +2096,12 @@
           <t>`Ryska II` → `RY1012` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>`RY1012` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
         </is>
@@ -1918,7 +2134,12 @@
           <t>`Ryska I` → `RY1004` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>`RY1004` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
         </is>
@@ -1951,7 +2172,12 @@
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25D</t>
         </is>
@@ -1984,7 +2210,12 @@
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25E</t>
         </is>
@@ -2017,7 +2248,12 @@
           <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>`SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
         </is>
@@ -2050,7 +2286,12 @@
           <t>`Spanska I` → `SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>`SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2YT</t>
         </is>
@@ -2083,7 +2324,12 @@
           <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>`SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
@@ -2116,7 +2362,12 @@
           <t>`Spanska I` → `SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>`SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KT</t>
         </is>
@@ -2149,7 +2400,12 @@
           <t>`Spanska I` → `SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>`SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KU</t>
         </is>
@@ -2182,7 +2438,12 @@
           <t>`Spanska I` → `SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>`SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KV</t>
         </is>
@@ -2215,7 +2476,12 @@
           <t>`Spanska I` → `SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>`SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
         </is>
@@ -2248,7 +2514,12 @@
           <t>`Spanska I` → `SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>`SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
         </is>
@@ -2281,7 +2552,12 @@
           <t>`Spanska I` → `SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>`SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1052</t>
         </is>
@@ -2314,7 +2590,12 @@
           <t>`Spanska I` → `SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>`SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1053</t>
         </is>
@@ -2347,7 +2628,12 @@
           <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>`SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2021</t>
         </is>
@@ -2380,7 +2666,12 @@
           <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>`SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2022</t>
         </is>
@@ -2413,7 +2704,12 @@
           <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>`SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2023</t>
         </is>
@@ -2446,7 +2742,12 @@
           <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>`SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
         </is>
@@ -2479,7 +2780,12 @@
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS257</t>
         </is>
@@ -2512,7 +2818,12 @@
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS258</t>
         </is>
@@ -2545,7 +2856,12 @@
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS28X</t>
         </is>
@@ -2578,7 +2894,12 @@
           <t>`Svenska som andraspråk` → `SSB001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>`SSB001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3004</t>
         </is>
@@ -2611,7 +2932,12 @@
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY255</t>
         </is>
@@ -2644,7 +2970,12 @@
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY256</t>
         </is>
@@ -2677,7 +3008,12 @@
           <t>`Tyskspråkig litteratur och litteraturvetenskap` → `TY2003` (nedlagd 2011-02-10); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>`TY2003` (nedlagd 2011-02-10); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
         </is>
@@ -2710,7 +3046,12 @@
           <t>`Den moderna tyskspråkiga lingvistikens utveckling` → `TYC002` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>`TYC002` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
         </is>
@@ -2743,7 +3084,12 @@
           <t>`Examensarbete` → `EN2004` (nedlagd 2011-02-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>`EN2004` (nedlagd 2011-02-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
         </is>
@@ -2776,7 +3122,12 @@
           <t>`Tyskspråkig litteratur och litteraturvetenskap` → `TY2003` (nedlagd 2011-02-10); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>`TY2003` (nedlagd 2011-02-10); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
         </is>
@@ -2809,7 +3160,12 @@
           <t>`Den moderna tyskspråkiga lingvistikens utveckling` → `TYC002` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>`TYC002` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
         </is>
@@ -2842,7 +3198,12 @@
           <t>`Examensarbete` → `EN2004` (nedlagd 2011-02-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>`EN2004` (nedlagd 2011-02-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
         </is>
@@ -2875,7 +3236,12 @@
           <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>`TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY23C</t>
         </is>
@@ -2908,7 +3274,12 @@
           <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>`TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
         </is>
@@ -2941,7 +3312,12 @@
           <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>`TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N4</t>
         </is>
@@ -2974,7 +3350,12 @@
           <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>`TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
         </is>
@@ -3007,7 +3388,12 @@
           <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>`TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J6</t>
         </is>
@@ -3040,7 +3426,12 @@
           <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>`TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J7</t>
         </is>
@@ -3073,7 +3464,12 @@
           <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>`TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J8</t>
         </is>
@@ -3110,7 +3506,12 @@
           <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>`TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1049</t>
         </is>
@@ -3147,7 +3548,12 @@
           <t>`Tysk grammatik med textkommentar` → `TYA038` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>`TYA038` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1050</t>
         </is>
@@ -3184,7 +3590,12 @@
           <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>`TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
         </is>
@@ -3217,7 +3628,8 @@
           <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Tysk grammatik och textkommentar'</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1069</t>
         </is>
@@ -3250,7 +3662,12 @@
           <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>`TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1073</t>
         </is>
@@ -3287,7 +3704,8 @@
           <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Muntlig språkfärdighet med kulturkunskap II'</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2004</t>
         </is>
@@ -3324,7 +3742,8 @@
           <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Muntlig språkfärdighet med kulturkunskap II'</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
         </is>
@@ -3361,7 +3780,12 @@
           <t>`Tyskspråkig skönlitteratur och litteraturhistoria` → `TYB013` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>`TYB013` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
         </is>
@@ -3398,189 +3822,190 @@
           <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Språk- och kulturhistoria med uppsats'</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G88"/>
+  <autoFilter ref="A1:H88"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId124"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId134"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId146"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId150"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId152"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId154"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId156"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId158"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId160"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId162"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId166"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId168"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId170"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId172"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId174"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Förkunskapskrav.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Förkunskapskrav.xlsx
@@ -515,7 +515,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>`Arabiska VII` → `AR1013` (nedlagd 2017-10-17); förkunskap nämner nedlagd kurs</t>
+          <t>`Arabiska VII`</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -553,7 +553,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori`</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori`</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>`Introduktionskurs i modern engelsk lingvistik` → `EN1044` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`Introduktionskurs i modern engelsk lingvistik`</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori`</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori`</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>`Engelska` → `ENC036` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Engelska`</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>`Engelska` → `ENC036` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Engelska`</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori`</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori`</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>`Franskspråkig litteratur I` → `FR1029` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
+          <t>`Franskspråkig litteratur I`</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>`Franskspråkig litteratur I` → `FR1029` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
+          <t>`Franskspråkig litteratur I`</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>`Franskspråkig litteratur I` → `FR1029` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
+          <t>`Franskspråkig litteratur I`</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>`Franskspråkig litteratur II` → `FR1072` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
+          <t>`Franskspråkig litteratur II`</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>`Franskspråkig litteratur II` → `FR1072` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
+          <t>`Franskspråkig litteratur II`</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>`Franskspråkig litteratur I` → `FR1029` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
+          <t>`Franskspråkig litteratur I`</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>`Franskspråkig litteratur II` → `FR1072` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
+          <t>`Franskspråkig litteratur II`</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>`Italienska B` → `ITB001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Italienska B`</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>`Italienska förr och nu` → `IT1026` (nedlagd 2023-12-21); förkunskap nämner nedlagd kurs</t>
+          <t>`Italienska förr och nu`</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>`Italienska B` → `ITB001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Italienska B`</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>`Italienska förr och nu` → `IT1026` (nedlagd 2023-12-21); förkunskap nämner nedlagd kurs</t>
+          <t>`Italienska förr och nu`</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>`Italienska C` → `ITC002` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Italienska C`</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>`Italiensk språkvetenskap` → `IT2005` (nedlagd 2023-12-21); förkunskap nämner nedlagd kurs</t>
+          <t>`Italiensk språkvetenskap`</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>`Japanska II` → `JP1007` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Japanska II`</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>`Japanska II` → `JP1007` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Japanska II`</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>`Japanska III` → `JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Japanska III`</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>`Japanska I` → `JP1001` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Japanska I`</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>`Japanska II` → `JP1007` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Japanska II`</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>`Japanska II` → `JP1007` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Japanska II`</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>`Japanska III` → `JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Japanska III`</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>`Japanska III` → `JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Japanska III`</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>`Japanska III` → `JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Japanska III`</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>`Japanska III` → `JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Japanska III`</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori`</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>`Kinesisk traditionell filosofi` → `KI2006` (nedlagd 2025-09-26); förkunskap nämner nedlagd kurs</t>
+          <t>`Kinesisk traditionell filosofi`</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>`Språkinlärning` → `EN3050` (nedlagd 2016-01-12); förkunskap nämner nedlagd kurs</t>
+          <t>`Språkinlärning`</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>`Ryska I` → `RY1004` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
+          <t>`Ryska I`</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>`Ryska I` → `RY1004` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
+          <t>`Ryska I`</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>`Ryska I` → `RY1004` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
+          <t>`Ryska I`</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>`Ryska II` → `RY1012` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
+          <t>`Ryska II`</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>`Ryska II` → `RY1012` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
+          <t>`Ryska II`</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>`Ryska II` → `RY1012` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
+          <t>`Ryska II`</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>`Ryska I` → `RY1004` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
+          <t>`Ryska I`</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori`</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori`</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`Spanska II`</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>`Spanska I` → `SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`Spanska I`</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`Spanska II`</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>`Spanska I` → `SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`Spanska I`</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>`Spanska I` → `SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`Spanska I`</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>`Spanska I` → `SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`Spanska I`</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>`Spanska I` → `SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`Spanska I`</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>`Spanska I` → `SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`Spanska I`</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>`Spanska I` → `SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`Spanska I`</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>`Spanska I` → `SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`Spanska I`</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`Spanska II`</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`Spanska II`</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`Spanska II`</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>`Spanska II` → `SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`Spanska II`</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori`</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori`</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori`</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>`Svenska som andraspråk` → `SSB001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Svenska som andraspråk`</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori`</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori`</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>`Tyskspråkig litteratur och litteraturvetenskap` → `TY2003` (nedlagd 2011-02-10); förkunskap nämner nedlagd kurs</t>
+          <t>`Tyskspråkig litteratur och litteraturvetenskap`</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>`Den moderna tyskspråkiga lingvistikens utveckling` → `TYC002` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Den moderna tyskspråkiga lingvistikens utveckling`</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>`Examensarbete` → `EN2004` (nedlagd 2011-02-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Examensarbete`</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>`Tyskspråkig litteratur och litteraturvetenskap` → `TY2003` (nedlagd 2011-02-10); förkunskap nämner nedlagd kurs</t>
+          <t>`Tyskspråkig litteratur och litteraturvetenskap`</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>`Den moderna tyskspråkiga lingvistikens utveckling` → `TYC002` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Den moderna tyskspråkiga lingvistikens utveckling`</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>`Examensarbete` → `EN2004` (nedlagd 2011-02-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Examensarbete`</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Tyska`</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Tyska`</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Tyska`</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Tyska`</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Tyska`</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Tyska`</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Tyska`</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Tyska`</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>`Tysk grammatik med textkommentar` → `TYA038` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Tysk grammatik med textkommentar`</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Tyska`</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>`Tyska` → `TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Tyska`</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>`Tyskspråkig skönlitteratur och litteraturhistoria` → `TYB013` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Tyskspråkig skönlitteratur och litteraturhistoria`</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">

--- a/vault-dalarna-university/04 ISLL/Analys/Förkunskapskrav.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Förkunskapskrav.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Förkunskapskrav" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$H$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$H$146</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H88"/>
+  <dimension ref="A1:H146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -684,7 +684,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>EN3070</t>
+          <t>EN3063</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -694,10 +694,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2015-03-12</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>2013-11-14</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2021-06-30</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -705,24 +709,24 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori`</t>
+          <t>`Litteraturvetenskapligt skrivande`</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`EN3065` (nedlagd 2021-06-29); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3070</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3063</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>EN3072</t>
+          <t>EN3070</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -732,14 +736,10 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2015-03-16</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2017-03-13</t>
-        </is>
-      </c>
+          <t>2015-03-12</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -747,24 +747,24 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>`Engelska`</t>
+          <t>`Vetenskapsteori`</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>`ENC036` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3072</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3070</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>EN3077</t>
+          <t>EN3072</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -774,10 +774,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>2015-03-16</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>2017-03-13</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -785,34 +789,34 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>`Engelska`</t>
+          <t>`Kandidatexamensarbete i lingvistik`</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>`ENC036` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`EN2015` (nedlagd 2016-01-12); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3077</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3072</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AFR24A</t>
+          <t>EN3077</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2017-03-13</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -823,24 +827,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori`</t>
+          <t>`Engelska`</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`ENC036` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3077</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AFR24B</t>
+          <t>AFR24A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -871,14 +875,14 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24A</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>GFR27N</t>
+          <t>AFR24B</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -888,7 +892,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2019-03-07</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -899,24 +903,24 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>`Franskspråkig litteratur I`</t>
+          <t>`Vetenskapsteori`</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>`FR1029` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
+          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24B</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>GFR27Q</t>
+          <t>GFR27N</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -947,14 +951,14 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27N</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>GFR27R</t>
+          <t>GFR27N</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -975,24 +979,24 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>`Franskspråkig litteratur I`</t>
+          <t>`Kultur och samhälle I`</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>`FR1029` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
+          <t>`GFR2AC` (nedlagd 2025-10-28); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27N</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>GFR2KQ</t>
+          <t>GFR27Q</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1002,7 +1006,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2020-11-11</t>
+          <t>2019-03-07</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1013,24 +1017,24 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>`Franskspråkig litteratur II`</t>
+          <t>`Franskspråkig litteratur I`</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>`FR1072` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
+          <t>`FR1029` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27Q</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GFR2KR</t>
+          <t>GFR27Q</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1040,7 +1044,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2020-11-11</t>
+          <t>2019-03-07</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1051,24 +1055,24 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>`Franskspråkig litteratur II`</t>
+          <t>`Kultur och samhälle I`</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>`FR1072` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
+          <t>`GFR2AC` (nedlagd 2025-10-28); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27Q</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GFR2R3</t>
+          <t>GFR27R</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1078,7 +1082,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2019-03-07</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1099,14 +1103,14 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27R</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GFR35F</t>
+          <t>GFR27R</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1116,7 +1120,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2019-03-07</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1127,41 +1131,37 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>`Franskspråkig litteratur II`</t>
+          <t>`Kultur och samhälle I`</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>`FR1072` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
+          <t>`GFR2AC` (nedlagd 2025-10-28); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR35F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27R</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GIT2GV</t>
+          <t>GFR2KQ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2020-06-03</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
+          <t>2020-11-11</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -1169,41 +1169,37 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>`Italienska B`</t>
+          <t>`Franskspråkig litteratur II`</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>`ITB001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`FR1072` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2GV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KQ</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GIT2GV</t>
+          <t>GFR2KQ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2020-06-03</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
+          <t>2020-11-11</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -1211,41 +1207,37 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>`Italienska förr och nu`</t>
+          <t>`Introduktion till lingvistik`</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>`IT1026` (nedlagd 2023-12-21); förkunskap nämner nedlagd kurs</t>
+          <t>`FR1089` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2GV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KQ</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GIT2GW</t>
+          <t>GFR2KQ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2020-06-03</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2023-12-18</t>
-        </is>
-      </c>
+          <t>2020-11-11</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -1253,41 +1245,37 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>`Italienska B`</t>
+          <t>`Kultur och samhälle II`</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>`ITB001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`GFR27P` (nedlagd 2025-10-28); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KQ</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GIT2GW</t>
+          <t>GFR2KR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2020-06-03</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2023-12-18</t>
-        </is>
-      </c>
+          <t>2020-11-11</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -1295,34 +1283,34 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>`Italienska förr och nu`</t>
+          <t>`Franskspråkig litteratur II`</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>`IT1026` (nedlagd 2023-12-21); förkunskap nämner nedlagd kurs</t>
+          <t>`FR1072` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KR</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GIT397</t>
+          <t>GFR2KR</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2023-12-20</t>
+          <t>2020-11-11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1333,34 +1321,34 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>`Italienska C`</t>
+          <t>`Introduktion till lingvistik`</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>`ITC002` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`FR1089` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT397</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KR</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GIT397</t>
+          <t>GFR2KR</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2023-12-20</t>
+          <t>2020-11-11</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1371,34 +1359,34 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>`Italiensk språkvetenskap`</t>
+          <t>`Kultur och samhälle II`</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>`IT2005` (nedlagd 2023-12-21); förkunskap nämner nedlagd kurs</t>
+          <t>`GFR27P` (nedlagd 2025-10-28); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT397</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KR</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GJP23L</t>
+          <t>GFR2R3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2018-08-23</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1409,34 +1397,34 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>`Japanska II`</t>
+          <t>`Franskspråkig litteratur I`</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>`JP1007` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+          <t>`FR1029` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GJP242</t>
+          <t>GFR2R3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2018-08-23</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1447,34 +1435,34 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>`Japanska II`</t>
+          <t>`Kultur och samhälle I`</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>`JP1007` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+          <t>`GFR2AC` (nedlagd 2025-10-28); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP242</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GJP243</t>
+          <t>GFR35F</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2018-08-23</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1485,34 +1473,34 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>`Japanska III`</t>
+          <t>`Franskspråkig litteratur II`</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>`JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+          <t>`FR1072` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP243</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR35F</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GJP2MZ</t>
+          <t>GFR35F</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1523,34 +1511,34 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>`Japanska I`</t>
+          <t>`Introduktion till lingvistik`</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>`JP1001` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+          <t>`FR1089` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR35F</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GJP2N2</t>
+          <t>GFR35F</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1561,37 +1549,41 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>`Japanska II`</t>
+          <t>`Kultur och samhälle II`</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>`JP1007` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+          <t>`GFR27P` (nedlagd 2025-10-28); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2N2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR35F</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GJP37U</t>
+          <t>GIT26V</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>2019-03-01</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -1599,37 +1591,41 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>`Japanska II`</t>
+          <t>`Fonetik och muntlig språkfärdighet`</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>`JP1007` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+          <t>`IT1030` (nedlagd 2023-12-21); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT26V</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GJP37W</t>
+          <t>GIT26V</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>2019-03-01</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -1637,37 +1633,41 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>`Japanska III`</t>
+          <t>`Grammatik och skriftlig språkfärdighet`</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>`JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+          <t>`IT1031` (nedlagd 2023-12-21); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT26V</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GJP39W</t>
+          <t>GIT26W</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2023-12-20</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>2019-03-01</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -1675,37 +1675,41 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>`Japanska III`</t>
+          <t>`Fonetik och muntlig språkfärdighet`</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>`JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+          <t>`IT1030` (nedlagd 2023-12-21); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT26W</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GJP39X</t>
+          <t>GIT26W</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2023-12-20</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>2019-03-01</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -1713,37 +1717,41 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>`Japanska III`</t>
+          <t>`Grammatik och skriftlig språkfärdighet`</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>`JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+          <t>`IT1031` (nedlagd 2023-12-21); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT26W</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GJP3B2</t>
+          <t>GIT2A3</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>2019-06-19</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -1751,37 +1759,41 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>`Japanska III`</t>
+          <t>`Fonetik och muntlig språkfärdighet`</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>`JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
+          <t>`IT1030` (nedlagd 2023-12-21); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP3B2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2A3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>AKI25K</t>
+          <t>GIT2A3</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2020-03-12</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>2019-06-19</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -1789,37 +1801,41 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori`</t>
+          <t>`Grammatik och skriftlig språkfärdighet`</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`IT1031` (nedlagd 2023-12-21); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI25K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2A3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GKI2QA</t>
+          <t>GIT2AE</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2021-05-26</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>2019-08-23</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -1827,37 +1843,41 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>`Kinesisk traditionell filosofi`</t>
+          <t>`Fonetik och muntlig språkfärdighet`</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>`KI2006` (nedlagd 2025-09-26); förkunskap nämner nedlagd kurs</t>
+          <t>`IT1030` (nedlagd 2023-12-21); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2QA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2AE</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GKI3CD</t>
+          <t>GIT2AE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>2019-08-23</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -1865,37 +1885,41 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>`Språkinlärning`</t>
+          <t>`Grammatik och skriftlig språkfärdighet`</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>`EN3050` (nedlagd 2016-01-12); förkunskap nämner nedlagd kurs</t>
+          <t>`IT1031` (nedlagd 2023-12-21); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2AE</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GRY285</t>
+          <t>GIT2GV</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2019-03-11</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>2020-06-03</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -1903,37 +1927,41 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>`Ryska I`</t>
+          <t>`Italienska B`</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>`RY1004` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
+          <t>`ITB001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY285</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2GV</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GRY28H</t>
+          <t>GIT2GV</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2019-03-14</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>2020-06-03</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -1941,37 +1969,41 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>`Ryska I`</t>
+          <t>`Italienska förr och nu`</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>`RY1004` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
+          <t>`IT1026` (nedlagd 2023-12-21); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2GV</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GRY28J</t>
+          <t>GIT2GW</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2019-03-14</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>2020-06-03</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -1979,37 +2011,41 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>`Ryska I`</t>
+          <t>`Italienska B`</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>`RY1004` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
+          <t>`ITB001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2GW</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GRY28K</t>
+          <t>GIT2GW</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2019-03-14</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>2020-06-03</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -2017,37 +2053,41 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>`Ryska II`</t>
+          <t>`Italienska förr och nu`</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>`RY1012` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
+          <t>`IT1026` (nedlagd 2023-12-21); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2GW</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GRY28L</t>
+          <t>GIT2T6</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2019-03-14</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>2021-12-21</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -2055,37 +2095,41 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>`Ryska II`</t>
+          <t>`Nybörjarkurs II`</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>`RY1012` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
+          <t>`IT1018` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2T6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GRY28U</t>
+          <t>GIT2TD</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2019-03-25</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>2021-12-21</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -2093,37 +2137,41 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>`Ryska II`</t>
+          <t>`Nybörjarkurs II`</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>`RY1012` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
+          <t>`IT1018` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TD</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GRY38S</t>
+          <t>GIT2TE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>2021-12-21</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -2131,37 +2179,41 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>`Ryska I`</t>
+          <t>`Nybörjarkurs II`</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>`RY1004` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
+          <t>`IT1018` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TE</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>ASP25D</t>
+          <t>GIT2TF</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
+          <t>2021-12-21</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -2169,37 +2221,41 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori`</t>
+          <t>`Nybörjarkurs II`</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`IT1018` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TF</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>ASP25E</t>
+          <t>GIT2TG</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>2021-12-21</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -2207,37 +2263,41 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori`</t>
+          <t>`Nybörjarkurs II`</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`IT1018` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TG</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GSP2KS</t>
+          <t>GIT2TH</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2020-11-20</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>2021-12-21</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -2245,37 +2305,41 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>`Spanska II`</t>
+          <t>`Nybörjarkurs II`</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>`SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`IT1018` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TH</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GSP2YT</t>
+          <t>GIT2TJ</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2022-11-29</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>2021-12-21</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -2283,37 +2347,41 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>`Spanska I`</t>
+          <t>`Nybörjarkurs II`</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>`SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`IT1018` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2YT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TJ</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>GIT2TK</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>2021-12-21</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -2321,37 +2389,41 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>`Spanska II`</t>
+          <t>`Nybörjarkurs II`</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>`SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`IT1018` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GSP3KT</t>
+          <t>GIT2TL</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>2021-12-21</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -2359,37 +2431,41 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>`Spanska I`</t>
+          <t>`Nybörjarkurs II`</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>`SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`IT1018` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TL</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GSP3KU</t>
+          <t>GIT2TM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>2021-12-21</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -2397,37 +2473,41 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>`Spanska I`</t>
+          <t>`Nybörjarkurs II`</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>`SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`IT1018` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TM</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GSP3KV</t>
+          <t>GIT2TN</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
+          <t>2021-12-21</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -2435,37 +2515,41 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>`Spanska I`</t>
+          <t>`Nybörjarkurs II`</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>`SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`IT1018` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TN</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>SP1050</t>
+          <t>GIT2TP</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2017-06-15</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>2021-12-21</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -2473,37 +2557,41 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>`Spanska I`</t>
+          <t>`Nybörjarkurs II`</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>`SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`IT1018` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TP</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>SP1051</t>
+          <t>GIT2TQ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2017-06-15</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>2021-12-21</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -2511,34 +2599,34 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>`Spanska I`</t>
+          <t>`Nybörjarkurs II`</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>`SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`IT1018` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TQ</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>SP1052</t>
+          <t>GIT397</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2017-06-15</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -2549,34 +2637,34 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>`Spanska I`</t>
+          <t>`Italienska C`</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>`SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`ITC002` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1052</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT397</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>SP1053</t>
+          <t>GIT397</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2017-06-15</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -2587,34 +2675,34 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>`Spanska I`</t>
+          <t>`Italiensk språkvetenskap`</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>`SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`IT2005` (nedlagd 2023-12-21); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1053</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT397</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>SP2021</t>
+          <t>GIT3KL</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2018-02-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -2625,34 +2713,34 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>`Spanska II`</t>
+          <t>`Nybörjarkurs II`</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>`SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`IT1018` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2021</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT3KL</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>SP2022</t>
+          <t>GIT3KM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2018-02-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -2663,34 +2751,34 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>`Spanska II`</t>
+          <t>`Nybörjarkurs II`</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>`SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`IT1018` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT3KM</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>SP2023</t>
+          <t>GIT3KN</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2018-02-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -2701,34 +2789,34 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>`Spanska II`</t>
+          <t>`Nybörjarkurs II`</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>`SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`IT1018` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT3KN</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>SP2024</t>
+          <t>GIT3KP</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2018-02-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -2739,34 +2827,34 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>`Spanska II`</t>
+          <t>`Fonetik och muntlig språkfärdighet`</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>`SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+          <t>`IT1030` (nedlagd 2023-12-21); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT3KP</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>ASS257</t>
+          <t>GIT3KP</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -2777,34 +2865,34 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori`</t>
+          <t>`Grammatik och skriftlig språkfärdighet`</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`IT1031` (nedlagd 2023-12-21); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS257</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT3KP</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>ASS258</t>
+          <t>GIT3KQ</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -2815,34 +2903,34 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori`</t>
+          <t>`Fonetik och muntlig språkfärdighet`</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`IT1030` (nedlagd 2023-12-21); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS258</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT3KQ</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>ASS28X</t>
+          <t>GIT3KQ</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -2853,34 +2941,34 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori`</t>
+          <t>`Grammatik och skriftlig språkfärdighet`</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`IT1031` (nedlagd 2023-12-21); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS28X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT3KQ</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>SS3004</t>
+          <t>GIT3KR</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2014-04-11</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -2891,34 +2979,34 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>`Svenska som andraspråk`</t>
+          <t>`Fonetik och muntlig språkfärdighet`</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>`SSB001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`IT1030` (nedlagd 2023-12-21); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT3KR</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>ATY255</t>
+          <t>GIT3KR</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -2929,34 +3017,34 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori`</t>
+          <t>`Grammatik och skriftlig språkfärdighet`</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`IT1031` (nedlagd 2023-12-21); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY255</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT3KR</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>ATY256</t>
+          <t>IT1034</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2018-02-15</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2967,34 +3055,34 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori`</t>
+          <t>`Nybörjarkurs I`</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`IT1020` (nedlagd 2020-02-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY256</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IT1034</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>ATY2B7</t>
+          <t>GJP23L</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2018-08-23</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -3005,34 +3093,34 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>`Tyskspråkig litteratur och litteraturvetenskap`</t>
+          <t>`Japanska II`</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>`TY2003` (nedlagd 2011-02-10); förkunskap nämner nedlagd kurs</t>
+          <t>`JP1007` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23L</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>ATY2B7</t>
+          <t>GJP242</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2018-08-23</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -3043,34 +3131,34 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>`Den moderna tyskspråkiga lingvistikens utveckling`</t>
+          <t>`Japanska II`</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>`TYC002` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`JP1007` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP242</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>ATY2B7</t>
+          <t>GJP243</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2018-08-23</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -3081,34 +3169,34 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>`Examensarbete`</t>
+          <t>`Japanska III`</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>`EN2004` (nedlagd 2011-02-01); förkunskap nämner nedlagd kurs</t>
+          <t>`JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP243</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>ATY2B8</t>
+          <t>GJP2MZ</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -3119,34 +3207,34 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>`Tyskspråkig litteratur och litteraturvetenskap`</t>
+          <t>`Japanska I`</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>`TY2003` (nedlagd 2011-02-10); förkunskap nämner nedlagd kurs</t>
+          <t>`JP1001` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>ATY2B8</t>
+          <t>GJP2N2</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -3157,34 +3245,34 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>`Den moderna tyskspråkiga lingvistikens utveckling`</t>
+          <t>`Japanska II`</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>`TYC002` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`JP1007` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2N2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>ATY2B8</t>
+          <t>GJP37U</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2023-12-04</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -3195,34 +3283,34 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>`Examensarbete`</t>
+          <t>`Japanska II`</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>`EN2004` (nedlagd 2011-02-01); förkunskap nämner nedlagd kurs</t>
+          <t>`JP1007` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37U</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GTY23C</t>
+          <t>GJP37V</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2018-06-05</t>
+          <t>2023-12-04</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -3233,34 +3321,34 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>`Tyska`</t>
+          <t>`Översättningens praktik`</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>`TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`AJP27X` (nedlagd 2025-09-26); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY23C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37V</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GTY2N3</t>
+          <t>GJP37W</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2023-12-04</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -3271,34 +3359,34 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>`Tyska`</t>
+          <t>`Japanska III`</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>`TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GTY2N4</t>
+          <t>GJP39W</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -3309,34 +3397,34 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>`Tyska`</t>
+          <t>`Japanska III`</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>`TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39W</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GTY3J5</t>
+          <t>GJP39X</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -3347,34 +3435,34 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>`Tyska`</t>
+          <t>`Japanska III`</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>`TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39X</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GTY3J6</t>
+          <t>GJP3B2</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -3385,34 +3473,34 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>`Tyska`</t>
+          <t>`Japanska III`</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>`TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`JP1012` (nedlagd 2009-12-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP3B2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GTY3J7</t>
+          <t>AKI25K</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2020-03-12</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -3423,34 +3511,34 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>`Tyska`</t>
+          <t>`Vetenskapsteori`</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>`TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI25K</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GTY3J8</t>
+          <t>GKI2QA</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -3461,41 +3549,37 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>`Tyska`</t>
+          <t>`Kinesisk traditionell filosofi`</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>`TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`KI2006` (nedlagd 2025-09-26); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2QA</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>TY1049</t>
+          <t>GKI3CD</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>2013-08-01</t>
-        </is>
-      </c>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -3503,41 +3587,37 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>`Tyska`</t>
+          <t>`Språkinlärning`</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>`TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`EN3050` (nedlagd 2016-01-12); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1049</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CD</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>TY1050</t>
+          <t>GPR256</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
+          <t>2018-10-10</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -3545,39 +3625,39 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>`Tysk grammatik med textkommentar`</t>
+          <t>`Vetenskaplig specialisering och fördjupning`</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>`TYA038` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`PR2006` (nedlagd 2025-09-26); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR256</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>TY1066</t>
+          <t>PR1017</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2013-11-04</t>
+          <t>2012-09-13</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2019-12-20</t>
+          <t>2016-04-14</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3587,71 +3667,83 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>`Tyska`</t>
+          <t>`Grammatik och skriftlig språkfärdighet I`</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>`TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`PR1023` (nedlagd 2025-09-26); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR1017</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>TY1069</t>
+          <t>PR1017</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2016-02-11</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
+          <t>2012-09-13</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2016-04-14</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Refererar troligen nedlagd kurs</t>
+          <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Tysk grammatik och textkommentar'</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr"/>
+          <t>`Fonetik och muntlig språkfärdighet I`</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>`PR1022` (nedlagd 2025-09-26); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1069</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR1017</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>TY1073</t>
+          <t>PR1024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2017-02-13</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
+          <t>2014-09-17</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2016-04-14</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -3659,117 +3751,121 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>`Tyska`</t>
+          <t>`Grammatik och skriftlig språkfärdighet I`</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>`TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`PR1023` (nedlagd 2025-09-26); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1073</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR1024</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>TY2004</t>
+          <t>PR2003</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2008-05-29</t>
+          <t>2012-10-31</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2013-08-01</t>
+          <t>2016-04-14</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Refererar troligen nedlagd kurs</t>
+          <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Muntlig språkfärdighet med kulturkunskap II'</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr"/>
+          <t>`Grammatik och skriftlig språkfärdighet II`</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>`PR1016` (nedlagd 2016-04-26); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2003</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>TY2007</t>
+          <t>PR2004</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
+          <t>2013-06-14</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2019-12-20</t>
+          <t>2016-04-14</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Refererar troligen nedlagd kurs</t>
+          <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Muntlig språkfärdighet med kulturkunskap II'</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr"/>
+          <t>`Grammatik och skriftlig språkfärdighet II`</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>`PR1016` (nedlagd 2016-04-26); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2004</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>TY2007</t>
+          <t>GRY285</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
+          <t>2019-03-11</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -3777,60 +3873,2292 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>`Tyskspråkig skönlitteratur och litteraturhistoria`</t>
+          <t>`Ryska I`</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>`TYB013` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+          <t>`RY1004` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY285</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>GRY28H</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2019-03-14</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>`Ryska I`</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>`RY1004` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28H</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>GRY28J</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2019-03-14</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>`Ryska I`</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>`RY1004` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28J</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>GRY28K</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2019-03-14</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>`Ryska II`</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>`RY1012` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28K</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>GRY28L</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2019-03-14</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>`Ryska II`</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>`RY1012` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28L</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>GRY28U</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2019-03-25</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>`Ryska II`</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>`RY1012` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>GRY38S</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>`Ryska I`</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>`RY1004` (nedlagd 2014-10-07); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>ASP25D</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>`Vetenskapsteori`</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25D</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>ASP25E</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>`Vetenskapsteori`</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25E</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>GSP2KS</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2020-11-20</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>`Spanska II`</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>`SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>GSP2YT</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2022-11-29</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>`Spanska I`</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>`SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2YT</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>GSP3GW</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>`Spanska II`</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>`SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>GSP3KT</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>`Spanska I`</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>`SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KT</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>GSP3KU</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>`Spanska I`</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>`SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>GSP3KV</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>`Spanska I`</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>`SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KV</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>SP1050</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2017-06-15</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>`Spanska I`</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>`SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>SP1051</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2017-06-15</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>`Spanska I`</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>`SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>SP1052</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2017-06-15</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>`Spanska I`</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>`SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1052</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>SP1053</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2017-06-15</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>`Spanska I`</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>`SP1014` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1053</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>SP2021</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2018-02-12</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>`Spanska II`</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>`SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>SP2022</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2018-02-12</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>`Spanska II`</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>`SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>SP2023</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2018-02-12</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>`Spanska II`</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>`SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>SP2024</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2018-02-12</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>`Spanska II`</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>`SP1001` (nedlagd 2020-05-05); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>ASS257</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>`Vetenskapsteori`</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS257</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>ASS258</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>`Vetenskapsteori`</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS258</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>ASS28X</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2023-05-22</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>`Arabiska I med didaktisk inriktning`</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>`GSS28D` (nedlagd 2026-02-16); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS28X</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>ASS28X</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2023-05-22</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>`Arabiska II med didaktisk inriktning`</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>`GSS2BM` (nedlagd 2026-02-16); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS28X</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>ASS28X</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2023-05-22</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>`Vetenskapsteori`</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS28X</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>GSS2GP</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>2020-04-27</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>`Arabiska I med didaktisk inriktning`</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>`GSS28D` (nedlagd 2026-02-16); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>GSS2GP</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2020-04-27</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>`Arabiska II med didaktisk inriktning`</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>`GSS2BM` (nedlagd 2026-02-16); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>GSS35H</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>`Arabiska I med didaktisk inriktning`</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>`GSS28D` (nedlagd 2026-02-16); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>SS3004</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2014-04-11</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>`Svenska som andraspråk`</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>`SSB001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3004</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>ATY255</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>`Vetenskapsteori`</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY255</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>ATY256</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>`Vetenskapsteori`</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY256</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>ATY2B7</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>`Tyskspråkig litteratur och litteraturvetenskap`</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>`TY2003` (nedlagd 2011-02-10); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>ATY2B7</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>`Den moderna tyskspråkiga lingvistikens utveckling`</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>`TYC002` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>ATY2B7</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>`Examensarbete`</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>`EN2004` (nedlagd 2011-02-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>ATY2B8</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>`Tyskspråkig litteratur och litteraturvetenskap`</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>`TY2003` (nedlagd 2011-02-10); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>ATY2B8</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>`Den moderna tyskspråkiga lingvistikens utveckling`</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>`TYC002` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>ATY2B8</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>`Examensarbete`</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>`EN2004` (nedlagd 2011-02-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>GTY23C</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>2018-06-05</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>`Tyska`</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>`TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY23C</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>GTY2N3</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>2021-03-04</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>`Tyska`</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>`TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>GTY2N4</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>2021-03-04</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>`Tyska`</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>`TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N4</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>GTY3J5</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>`Tyska`</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>`TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>GTY3J5</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>`Tysk grammatik`</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>`GTY2GM` (nedlagd 2025-10-06); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>GTY3J6</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>`Tyska`</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>`TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J6</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>GTY3J6</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>`Tysk grammatik`</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>`GTY2GM` (nedlagd 2025-10-06); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J6</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>GTY3J7</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>`Muntlig språkfärdighet med fonetik och kulturkunskap I`</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>`TY1072` (nedlagd 2025-10-06); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J7</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>GTY3J8</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>`Tyska`</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>`TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J8</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>TY1049</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2013-08-01</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>`Tyska`</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>`TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1049</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>TY1050</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>`Tysk grammatik med textkommentar`</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>`TYA038` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1050</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>TY1066</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>2013-11-04</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>`Tyska`</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>`TYC001` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>TY1069</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>2016-02-11</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Refererar troligen nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Tysk grammatik och textkommentar'</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1069</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>TY1069</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2016-02-11</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>`Tysk grammatik`</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>`GTY2GM` (nedlagd 2025-10-06); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1069</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>TY1073</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2017-02-13</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>`Muntlig språkfärdighet med fonetik och kulturkunskap I`</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>`TY1072` (nedlagd 2025-10-06); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1073</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>TY2004</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2008-05-29</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2013-08-01</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>`Muntlig språkfärdighet med kulturkunskap II`</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>`TY1004` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2004</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>TY2007</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>`Muntlig språkfärdighet med kulturkunskap II`</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>`TY1004` (nedlagd 2019-06-04); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>TY2007</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>`Språk- och kulturhistoria med uppsats`</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>`TY1048` (nedlagd 2021-02-23); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>TY2007</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>`Tyskspråkig skönlitteratur och litteraturhistoria`</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>`TYB013` (nedlagd 2008-09-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
           <t>TY2008</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B146" t="inlineStr">
         <is>
           <t>TYA</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C146" t="inlineStr">
         <is>
           <t>2012-05-21</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D146" t="inlineStr">
         <is>
           <t>2019-12-20</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Refererar troligen nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Språk- och kulturhistoria med uppsats'</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>`Språk- och kulturhistoria med uppsats`</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>`TY1048` (nedlagd 2021-02-23); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H88"/>
+  <autoFilter ref="A1:H146"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId2"/>
@@ -4006,6 +6334,122 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId172"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H107" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H108" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H109" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H110" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H111" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H112" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H113" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H114" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H118" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H119" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H123" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H124" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H125" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A132" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H132" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H133" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H136" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A137" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A138" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A139" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H139" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A140" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A141" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H141" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A142" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H142" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A144" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H144" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A145" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H145" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A146" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId290"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
